--- a/自然（しぜん）.xlsx
+++ b/自然（しぜん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="天気（てんき）" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="446">
   <si>
     <t>雨</t>
   </si>
@@ -1114,6 +1114,12 @@
     <t>ごとう</t>
   </si>
   <si>
+    <t>山林</t>
+  </si>
+  <si>
+    <t>さんりん</t>
+  </si>
+  <si>
     <t>山</t>
   </si>
   <si>
@@ -1417,6 +1423,35 @@
   </si>
   <si>
     <t>しゅう</t>
+  </si>
+  <si>
+    <t>鉱物</t>
+  </si>
+  <si>
+    <t>こうぶつ</t>
+  </si>
+  <si>
+    <r>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>矿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>物）</t>
+    </r>
   </si>
   <si>
     <t>日陰</t>
@@ -3430,7 +3465,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="4" width="16.1111111111111" customWidth="1"/>
@@ -3770,6 +3805,14 @@
       </c>
       <c r="K24" s="1" t="s">
         <v>327</v>
+      </c>
+    </row>
+    <row r="25" spans="10:12">
+      <c r="J25" t="s">
+        <v>328</v>
+      </c>
+      <c r="K25" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -3793,434 +3836,443 @@
     <row r="1" ht="17.4" customHeight="1"/>
     <row r="2" ht="39.6" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/自然（しぜん）.xlsx
+++ b/自然（しぜん）.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="465">
   <si>
     <t>雨</t>
   </si>
@@ -217,16 +217,37 @@
     <t>ざつおん</t>
   </si>
   <si>
+    <t>嵐</t>
+  </si>
+  <si>
+    <t>あらし</t>
+  </si>
+  <si>
+    <t>蒸し暑い</t>
+  </si>
+  <si>
+    <t>むしあつい</t>
+  </si>
+  <si>
+    <t>密やか</t>
+  </si>
+  <si>
+    <t>ひそやか</t>
+  </si>
+  <si>
     <t>小雨</t>
   </si>
   <si>
     <t>こさめ</t>
   </si>
   <si>
-    <t>蒸し暑い</t>
-  </si>
-  <si>
-    <t>むしあつい</t>
+    <t>湿潤</t>
+  </si>
+  <si>
+    <t>しつじゅん</t>
+  </si>
+  <si>
+    <t>湿潤気候｜しつじゅんきこう</t>
   </si>
   <si>
     <t>夕立</t>
@@ -238,15 +259,6 @@
     <t>（夏天傍晚的雷阵雨）</t>
   </si>
   <si>
-    <t>湿潤</t>
-  </si>
-  <si>
-    <t>しつじゅん</t>
-  </si>
-  <si>
-    <t>湿潤気候｜しつじゅんきこう</t>
-  </si>
-  <si>
     <t>雨水</t>
   </si>
   <si>
@@ -272,6 +284,18 @@
   </si>
   <si>
     <t>もうしょ</t>
+  </si>
+  <si>
+    <t>夜空</t>
+  </si>
+  <si>
+    <t>よぞら</t>
+  </si>
+  <si>
+    <t>夜明け</t>
+  </si>
+  <si>
+    <t>よあけ</t>
   </si>
   <si>
     <t>自然</t>
@@ -349,16 +373,22 @@
     <t>じょうき</t>
   </si>
   <si>
-    <t>夜空</t>
-  </si>
-  <si>
-    <t>よぞら</t>
-  </si>
-  <si>
-    <t>夜明け</t>
-  </si>
-  <si>
-    <t>よあけ</t>
+    <t>水蒸気</t>
+  </si>
+  <si>
+    <t>すいじょうき</t>
+  </si>
+  <si>
+    <t>防災</t>
+  </si>
+  <si>
+    <t>ぼうさい</t>
+  </si>
+  <si>
+    <t>防災訓練</t>
+  </si>
+  <si>
+    <t>ぼうさいくんれん</t>
   </si>
   <si>
     <t>四季（しき）</t>
@@ -428,6 +458,12 @@
   </si>
   <si>
     <t>しゅんかしゅうとう</t>
+  </si>
+  <si>
+    <t>秋分</t>
+  </si>
+  <si>
+    <t>しゅうぶん</t>
   </si>
   <si>
     <t>野生動物（やせいどうぶつ）</t>
@@ -696,6 +732,12 @@
     <t>きょうりゅう</t>
   </si>
   <si>
+    <t>雀</t>
+  </si>
+  <si>
+    <t>すずめ</t>
+  </si>
+  <si>
     <t>猿</t>
   </si>
   <si>
@@ -784,6 +826,15 @@
   </si>
   <si>
     <t>くさ</t>
+  </si>
+  <si>
+    <t>田植え</t>
+  </si>
+  <si>
+    <t>たうえ</t>
+  </si>
+  <si>
+    <t>（稻苗移栽到水田的农活）</t>
   </si>
   <si>
     <t>茄子</t>
@@ -1432,6 +1483,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（</t>
     </r>
     <r>
@@ -1539,6 +1596,12 @@
   </si>
   <si>
     <t>みね</t>
+  </si>
+  <si>
+    <t>緯度</t>
+  </si>
+  <si>
+    <t>いど</t>
   </si>
 </sst>
 </file>
@@ -1761,14 +1824,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2555,7 +2618,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:L29"/>
+  <dimension ref="A2:L31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
@@ -2766,164 +2829,202 @@
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="1"/>
       <c r="E11" s="1" t="s">
         <v>61</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="H11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>65</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" ht="18" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" ht="18" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2935,8 +3036,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.55555555555556" customWidth="1"/>
     <col min="3" max="3" width="16.1111111111111" customWidth="1"/>
@@ -2944,85 +3045,93 @@
   <sheetData>
     <row r="1" ht="18" spans="1:4">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3058,7 +3167,7 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -3070,308 +3179,314 @@
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="6" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="37.2" customHeight="1" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" ht="27.6" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G7" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="G9" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="E11" s="1" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="E12" s="1" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="E13" s="1" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="I13" t="s">
+        <v>218</v>
+      </c>
+      <c r="J13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="E14" s="1" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="E15" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="17" ht="35.4" customHeight="1" spans="1:12">
       <c r="A17" s="9" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -3381,75 +3496,75 @@
     </row>
     <row r="18" ht="18" spans="1:12">
       <c r="A18" s="6" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C19" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:12">
@@ -3465,354 +3580,363 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="4" width="16.1111111111111" customWidth="1"/>
     <col min="10" max="10" width="9.55555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:12">
+    <row r="1" ht="18" spans="1:16">
       <c r="G1" s="1" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="K1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="2" ht="18" spans="1:12">
+        <v>249</v>
+      </c>
+      <c r="N1" t="s">
+        <v>250</v>
+      </c>
+      <c r="O1" t="s">
+        <v>251</v>
+      </c>
+      <c r="P1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="3" ht="18" spans="1:12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" ht="18" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="4" ht="18" spans="1:12">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" ht="18" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="5" ht="18" spans="1:12">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" ht="18" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="6" ht="18" spans="1:12">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" ht="18" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7" ht="18" spans="1:12">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7" ht="18" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="8" ht="18" spans="1:12">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="D8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="9" ht="18" spans="1:12">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="10" ht="18" spans="1:12">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" ht="18" spans="1:16">
       <c r="J10" s="1" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="12" ht="18" spans="1:12">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" ht="18" spans="1:16">
       <c r="J12" s="1" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" ht="18" spans="1:12">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="1:16">
       <c r="J13" s="1" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="14" ht="18" spans="1:12">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="14" ht="18" spans="1:16">
       <c r="J14" s="1" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="15" ht="18" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" ht="18" spans="1:16">
       <c r="J15" s="1" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="16" ht="18" spans="1:12">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="16" ht="18" spans="1:16">
       <c r="J16" s="1" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" ht="18" spans="10:12">
       <c r="J17" s="1" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" ht="18" spans="10:12">
       <c r="J18" s="1" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" ht="18" spans="10:12">
       <c r="J19" s="1" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20" ht="18" spans="10:12">
       <c r="J20" s="1" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="L20" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" ht="18" spans="10:12">
       <c r="J21" s="1" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" ht="18" spans="10:12">
       <c r="J22" s="1" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="L22" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" ht="18" spans="10:12">
       <c r="J23" s="1" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" ht="18" spans="10:12">
       <c r="J24" s="1" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="10:12">
       <c r="J25" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="K25" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -3824,7 +3948,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="5" width="8.88888888888889" style="1"/>
@@ -3836,443 +3960,451 @@
     <row r="1" ht="17.4" customHeight="1"/>
     <row r="2" ht="39.6" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="3" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>445</v>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/自然（しぜん）.xlsx
+++ b/自然（しぜん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="18288" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="天気（てんき）" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="469">
   <si>
     <t>雨</t>
   </si>
@@ -1042,6 +1042,12 @@
     <t>にんじん</t>
   </si>
   <si>
+    <t>麻</t>
+  </si>
+  <si>
+    <t>あさ</t>
+  </si>
+  <si>
     <t>枇榔</t>
   </si>
   <si>
@@ -1274,25 +1280,22 @@
     <t>じゅんかん</t>
   </si>
   <si>
+    <t>滝</t>
+  </si>
+  <si>
+    <t>たき</t>
+  </si>
+  <si>
+    <t>災害</t>
+  </si>
+  <si>
+    <t>さいがい</t>
+  </si>
+  <si>
     <t>江</t>
   </si>
   <si>
     <t>え、こう</t>
-  </si>
-  <si>
-    <t>災害</t>
-  </si>
-  <si>
-    <t>さいがい</t>
-  </si>
-  <si>
-    <t>湖</t>
-  </si>
-  <si>
-    <t>うみ</t>
-  </si>
-  <si>
-    <t>かい</t>
   </si>
   <si>
     <t>被害</t>
@@ -1330,13 +1333,31 @@
     </r>
   </si>
   <si>
+    <t>湖</t>
+  </si>
+  <si>
+    <t>うみ</t>
+  </si>
+  <si>
+    <t>かい</t>
+  </si>
+  <si>
+    <t>天変地異</t>
+  </si>
+  <si>
+    <t>てんぺんちい</t>
+  </si>
+  <si>
     <t>海</t>
   </si>
   <si>
-    <t>天変地異</t>
-  </si>
-  <si>
-    <t>てんぺんちい</t>
+    <t>合流</t>
+  </si>
+  <si>
+    <t>ごうりゅう</t>
+  </si>
+  <si>
+    <t>（河流合流，人会合）</t>
   </si>
   <si>
     <t>潮</t>
@@ -1345,22 +1366,19 @@
     <t>しお</t>
   </si>
   <si>
-    <t>合流</t>
-  </si>
-  <si>
-    <t>ごうりゅう</t>
-  </si>
-  <si>
-    <t>（河流合流，人会合）</t>
+    <t>温室</t>
+  </si>
+  <si>
+    <t>おんしつ</t>
   </si>
   <si>
     <t>汐</t>
   </si>
   <si>
-    <t>温室</t>
-  </si>
-  <si>
-    <t>おんしつ</t>
+    <t>温室効果</t>
+  </si>
+  <si>
+    <t>おんしつこうか</t>
   </si>
   <si>
     <t>海峡</t>
@@ -1369,10 +1387,10 @@
     <t>かいきょう</t>
   </si>
   <si>
-    <t>温室効果</t>
-  </si>
-  <si>
-    <t>おんしつこうか</t>
+    <t>自然法則</t>
+  </si>
+  <si>
+    <t>しぜんほうそく</t>
   </si>
   <si>
     <t>岬</t>
@@ -1381,10 +1399,10 @@
     <t>みさき</t>
   </si>
   <si>
-    <t>自然法則</t>
-  </si>
-  <si>
-    <t>しぜんほうそく</t>
+    <t>予備電源</t>
+  </si>
+  <si>
+    <t>よびでんげん</t>
   </si>
   <si>
     <t>海岸</t>
@@ -1393,10 +1411,10 @@
     <t>かいがん</t>
   </si>
   <si>
-    <t>予備電源</t>
-  </si>
-  <si>
-    <t>よびでんげん</t>
+    <t>回収</t>
+  </si>
+  <si>
+    <t>かいしゅう</t>
   </si>
   <si>
     <t>沿岸</t>
@@ -1405,10 +1423,10 @@
     <t>えんがん</t>
   </si>
   <si>
-    <t>回収</t>
-  </si>
-  <si>
-    <t>かいしゅう</t>
+    <t>浄水</t>
+  </si>
+  <si>
+    <t>じょうすい</t>
   </si>
   <si>
     <t>月光</t>
@@ -1417,28 +1435,16 @@
     <t>げっこう</t>
   </si>
   <si>
-    <t>浄水</t>
-  </si>
-  <si>
-    <t>じょうすい</t>
+    <t>淡水</t>
+  </si>
+  <si>
+    <t>たんすい</t>
   </si>
   <si>
     <t>土</t>
   </si>
   <si>
     <t>つち</t>
-  </si>
-  <si>
-    <t>淡水</t>
-  </si>
-  <si>
-    <t>たんすい</t>
-  </si>
-  <si>
-    <t>土壌</t>
-  </si>
-  <si>
-    <t>どじょう</t>
   </si>
   <si>
     <r>
@@ -1470,10 +1476,10 @@
     </r>
   </si>
   <si>
-    <t>州</t>
-  </si>
-  <si>
-    <t>しゅう</t>
+    <t>土壌</t>
+  </si>
+  <si>
+    <t>どじょう</t>
   </si>
   <si>
     <t>鉱物</t>
@@ -1509,6 +1515,12 @@
       </rPr>
       <t>物）</t>
     </r>
+  </si>
+  <si>
+    <t>州</t>
+  </si>
+  <si>
+    <t>しゅう</t>
   </si>
   <si>
     <t>日陰</t>
@@ -3773,151 +3785,156 @@
       <c r="B8" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" t="s">
+        <v>305</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="J10" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="J12" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="J13" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="J14" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="J15" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="J16" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" ht="18" spans="10:12">
       <c r="J17" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" ht="18" spans="10:12">
       <c r="J18" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" ht="18" spans="10:12">
       <c r="J19" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" ht="18" spans="10:12">
       <c r="J20" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L20" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" ht="18" spans="10:12">
       <c r="J21" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" ht="18" spans="10:12">
       <c r="J22" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L22" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" ht="18" spans="10:12">
       <c r="J23" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>301</v>
@@ -3925,18 +3942,18 @@
     </row>
     <row r="24" ht="18" spans="10:12">
       <c r="J24" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="10:12">
       <c r="J25" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K25" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -3948,7 +3965,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="5" width="8.88888888888889" style="1"/>
@@ -3960,451 +3977,459 @@
     <row r="1" ht="17.4" customHeight="1"/>
     <row r="2" ht="39.6" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>386</v>
+        <v>393</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>373</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>436</v>
+        <v>374</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>437</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="3" t="s">
-        <v>441</v>
+      <c r="A27" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="1" t="s">
-        <v>443</v>
+      <c r="A28" s="3" t="s">
+        <v>445</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/自然（しぜん）.xlsx
+++ b/自然（しぜん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18288" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="天気（てんき）" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="479">
   <si>
     <t>雨</t>
   </si>
@@ -284,6 +284,18 @@
   </si>
   <si>
     <t>もうしょ</t>
+  </si>
+  <si>
+    <t>快晴</t>
+  </si>
+  <si>
+    <t>かいせい</t>
+  </si>
+  <si>
+    <t>晴天</t>
+  </si>
+  <si>
+    <t>せいてん</t>
   </si>
   <si>
     <t>夜空</t>
@@ -1175,6 +1187,24 @@
   </si>
   <si>
     <t>さんりん</t>
+  </si>
+  <si>
+    <t>桜並木</t>
+  </si>
+  <si>
+    <t>さくらなみき</t>
+  </si>
+  <si>
+    <t>（樱花大道）</t>
+  </si>
+  <si>
+    <t>並木</t>
+  </si>
+  <si>
+    <t>なみ</t>
+  </si>
+  <si>
+    <t>（街道旁的树）</t>
   </si>
   <si>
     <t>山</t>
@@ -1836,14 +1866,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2630,7 +2660,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:L31"/>
+  <dimension ref="A2:L33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
@@ -2924,19 +2954,19 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" ht="18" spans="1:3">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" ht="18" spans="1:3">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3003,31 +3033,31 @@
       <c r="B27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="29" ht="18" spans="1:3">
+      <c r="A29" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
+      <c r="B29" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
+    <row r="30" ht="18" spans="1:3">
+      <c r="A30" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3037,6 +3067,22 @@
       </c>
       <c r="B31" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3057,93 +3103,93 @@
   <sheetData>
     <row r="1" ht="18" spans="1:4">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3179,7 +3225,7 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -3191,314 +3237,314 @@
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" ht="37.2" customHeight="1" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" ht="27.6" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G9" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="E11" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="E12" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="E13" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I13" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="J13" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="E14" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="E15" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="17" ht="35.4" customHeight="1" spans="1:12">
       <c r="A17" s="9" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -3508,75 +3554,75 @@
     </row>
     <row r="18" ht="18" spans="1:12">
       <c r="A18" s="6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C19" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:12">
@@ -3592,7 +3638,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="4" width="16.1111111111111" customWidth="1"/>
@@ -3601,359 +3647,381 @@
   <sheetData>
     <row r="1" ht="18" spans="1:16">
       <c r="G1" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="O1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="P1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="J10" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="J12" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="J13" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="J14" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="J15" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="J16" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" ht="18" spans="10:12">
       <c r="J17" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" ht="18" spans="10:12">
       <c r="J18" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" ht="18" spans="10:12">
       <c r="J19" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" ht="18" spans="10:12">
       <c r="J20" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L20" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" ht="18" spans="10:12">
       <c r="J21" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" ht="18" spans="10:12">
       <c r="J22" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="L22" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" ht="18" spans="10:12">
       <c r="J23" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" ht="18" spans="10:12">
       <c r="J24" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="10:12">
       <c r="J25" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K25" t="s">
-        <v>348</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="26" spans="10:12">
+      <c r="J26" t="s">
+        <v>353</v>
+      </c>
+      <c r="K26" t="s">
+        <v>354</v>
+      </c>
+      <c r="L26" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="27" spans="10:12">
+      <c r="J27" t="s">
+        <v>356</v>
+      </c>
+      <c r="K27" t="s">
+        <v>357</v>
+      </c>
+      <c r="L27" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3977,459 +4045,459 @@
     <row r="1" ht="17.4" customHeight="1"/>
     <row r="2" ht="39.6" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="3" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/自然（しぜん）.xlsx
+++ b/自然（しぜん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="天気（てんき）" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="488">
   <si>
     <t>雨</t>
   </si>
@@ -1078,6 +1078,15 @@
     <t>こしょう</t>
   </si>
   <si>
+    <t>繊維</t>
+  </si>
+  <si>
+    <t>せんい</t>
+  </si>
+  <si>
+    <t>（纤维）</t>
+  </si>
+  <si>
     <t>苺</t>
   </si>
   <si>
@@ -1644,6 +1653,24 @@
   </si>
   <si>
     <t>いど</t>
+  </si>
+  <si>
+    <t>高度</t>
+  </si>
+  <si>
+    <t>こうど</t>
+  </si>
+  <si>
+    <t>海抜</t>
+  </si>
+  <si>
+    <t>かいばつ</t>
+  </si>
+  <si>
+    <t>引力</t>
+  </si>
+  <si>
+    <t>いんりょく</t>
   </si>
 </sst>
 </file>
@@ -3857,130 +3884,139 @@
       <c r="B9" s="1" t="s">
         <v>315</v>
       </c>
+      <c r="D9" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" t="s">
+        <v>318</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="J10" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="J12" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="J13" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="J14" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="J15" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="J16" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" ht="18" spans="10:12">
       <c r="J17" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" ht="18" spans="10:12">
       <c r="J18" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" ht="18" spans="10:12">
       <c r="J19" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" ht="18" spans="10:12">
       <c r="J20" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L20" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" ht="18" spans="10:12">
       <c r="J21" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" ht="18" spans="10:12">
       <c r="J22" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L22" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" ht="18" spans="10:12">
       <c r="J23" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>305</v>
@@ -3988,40 +4024,40 @@
     </row>
     <row r="24" ht="18" spans="10:12">
       <c r="J24" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="10:12">
       <c r="J25" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="10:12">
       <c r="J26" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K26" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L26" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="10:12">
       <c r="J27" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K27" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L27" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -4033,7 +4069,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="5" width="8.88888888888889" style="1"/>
@@ -4045,459 +4081,483 @@
     <row r="1" ht="17.4" customHeight="1"/>
     <row r="2" ht="39.6" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/自然（しぜん）.xlsx
+++ b/自然（しぜん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="天気（てんき）" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="495">
   <si>
     <t>雨</t>
   </si>
@@ -259,6 +259,12 @@
     <t>（夏天傍晚的雷阵雨）</t>
   </si>
   <si>
+    <t>低温</t>
+  </si>
+  <si>
+    <t>ていおん</t>
+  </si>
+  <si>
     <t>雨水</t>
   </si>
   <si>
@@ -302,6 +308,15 @@
   </si>
   <si>
     <t>よぞら</t>
+  </si>
+  <si>
+    <t>陽光</t>
+  </si>
+  <si>
+    <t>ようこう</t>
+  </si>
+  <si>
+    <t>太陽｜たいよう</t>
   </si>
   <si>
     <t>夜明け</t>
@@ -401,6 +416,18 @@
   </si>
   <si>
     <t>ぼうさいくんれん</t>
+  </si>
+  <si>
+    <t>空中</t>
+  </si>
+  <si>
+    <t>くうちゅう</t>
+  </si>
+  <si>
+    <t>陸地</t>
+  </si>
+  <si>
+    <t>りくち</t>
   </si>
   <si>
     <t>四季（しき）</t>
@@ -1599,12 +1626,6 @@
   </si>
   <si>
     <t>たいようこう</t>
-  </si>
-  <si>
-    <t>陽光</t>
-  </si>
-  <si>
-    <t>ようこう</t>
   </si>
   <si>
     <t>太陽系</t>
@@ -1893,14 +1914,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2687,7 +2708,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:L33"/>
+  <dimension ref="A2:L36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
@@ -2945,171 +2966,204 @@
       <c r="C13" t="s">
         <v>72</v>
       </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="14" ht="18" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" t="s">
         <v>110</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" ht="18" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3130,93 +3184,93 @@
   <sheetData>
     <row r="1" ht="18" spans="1:4">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3252,7 +3306,7 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -3264,314 +3318,314 @@
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="6" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" ht="37.2" customHeight="1" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" ht="27.6" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="G8" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="G9" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="E11" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="E12" s="1" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="E13" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="I13" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="J13" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="E14" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="E15" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="17" ht="35.4" customHeight="1" spans="1:12">
       <c r="A17" s="9" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -3581,75 +3635,75 @@
     </row>
     <row r="18" ht="18" spans="1:12">
       <c r="A18" s="6" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C19" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:12">
@@ -3674,390 +3728,390 @@
   <sheetData>
     <row r="1" ht="18" spans="1:16">
       <c r="G1" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="K1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="N1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="O1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="P1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D9" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="E9" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="F9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="J10" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="J12" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="J13" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="J14" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="J15" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="J16" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" ht="18" spans="10:12">
       <c r="J17" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" ht="18" spans="10:12">
       <c r="J18" s="1" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" ht="18" spans="10:12">
       <c r="J19" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" ht="18" spans="10:12">
       <c r="J20" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="L20" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" ht="18" spans="10:12">
       <c r="J21" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" ht="18" spans="10:12">
       <c r="J22" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="L22" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" ht="18" spans="10:12">
       <c r="J23" s="1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" ht="18" spans="10:12">
       <c r="J24" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" spans="10:12">
       <c r="J25" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="K25" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="10:12">
       <c r="J26" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="K26" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="L26" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="10:12">
       <c r="J27" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="K27" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="L27" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -4081,483 +4135,483 @@
     <row r="1" ht="17.4" customHeight="1"/>
     <row r="2" ht="39.6" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="3" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>464</v>
+        <v>90</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>465</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
